--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.36837387817731</v>
+        <v>5.584860755203813</v>
       </c>
       <c r="D2" t="n">
-        <v>7.404870561419875</v>
+        <v>1.20329146623073</v>
       </c>
       <c r="E2" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F2" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.56131485858484</v>
+        <v>3.341213664520036</v>
       </c>
       <c r="D3" t="n">
-        <v>5.923252221864551</v>
+        <v>0.9625284860529896</v>
       </c>
       <c r="E3" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F3" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.50610610512878</v>
+        <v>4.794742242083426</v>
       </c>
       <c r="D4" t="n">
-        <v>28.6144656629941</v>
+        <v>4.649850670236542</v>
       </c>
       <c r="E4" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F4" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.98281929548951</v>
+        <v>2.922208135517046</v>
       </c>
       <c r="D5" t="n">
-        <v>11.65469914475884</v>
+        <v>1.893888611023311</v>
       </c>
       <c r="E5" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F5" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.10243210551524</v>
+        <v>2.454145217146227</v>
       </c>
       <c r="D6" t="n">
-        <v>14.27659744330536</v>
+        <v>2.31994708453712</v>
       </c>
       <c r="E6" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F6" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.15469834252776</v>
+        <v>4.737638480660761</v>
       </c>
       <c r="D7" t="n">
-        <v>31.04829051830457</v>
+        <v>5.045347209224493</v>
       </c>
       <c r="E7" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F7" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.806620163622007</v>
+        <v>1.431075776588576</v>
       </c>
       <c r="D8" t="n">
-        <v>5.267516441881916</v>
+        <v>0.8559714218058113</v>
       </c>
       <c r="E8" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F8" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.88526215273524</v>
+        <v>3.718855099819477</v>
       </c>
       <c r="D9" t="n">
-        <v>19.26562970617497</v>
+        <v>3.130664827253432</v>
       </c>
       <c r="E9" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F9" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.66740078969273</v>
+        <v>3.683452628325069</v>
       </c>
       <c r="D10" t="n">
-        <v>17.60195856783843</v>
+        <v>2.860318267273746</v>
       </c>
       <c r="E10" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F10" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.63620921071873</v>
+        <v>2.703383996741794</v>
       </c>
       <c r="D11" t="n">
-        <v>16.53919414293812</v>
+        <v>2.687619048227445</v>
       </c>
       <c r="E11" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F11" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.78464585965649</v>
+        <v>2.40250495219418</v>
       </c>
       <c r="D12" t="n">
-        <v>7.44537933683622</v>
+        <v>1.209874142235886</v>
       </c>
       <c r="E12" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F12" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.69132737577609</v>
+        <v>2.712340698563615</v>
       </c>
       <c r="D13" t="n">
-        <v>11.89043962434589</v>
+        <v>1.932196438956207</v>
       </c>
       <c r="E13" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F13" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.66916342685172</v>
+        <v>1.896239056863404</v>
       </c>
       <c r="D14" t="n">
-        <v>6.781744948512153</v>
+        <v>1.102033554133225</v>
       </c>
       <c r="E14" t="n">
-        <v>7.171205223373047</v>
+        <v>1.16532084879812</v>
       </c>
       <c r="F14" t="n">
-        <v>8.044245873480799</v>
+        <v>1.30718995444063</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
